--- a/FAI Project Tracker.xlsx
+++ b/FAI Project Tracker.xlsx
@@ -3,21 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{90E58032-956C-4E9C-9C71-84D9E23ACC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09543A0E-64BA-4B14-A7E9-572D4532E679}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="8_{90E58032-956C-4E9C-9C71-84D9E23ACC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CDF4CC8-BAF0-4CE5-979D-119E71111B5A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="To Do List" sheetId="1" r:id="rId1"/>
-    <sheet name="Settings &amp; Calculations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="HighlightActivities">'To Do List'!$G$5</definedName>
-    <definedName name="lstToDoHighlights">'Settings &amp; Calculations'!$E$5:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'To Do List'!$A$1:$H$17</definedName>
+    <definedName name="lstToDoHighlights">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'To Do List'!$A$1:$H$22</definedName>
     <definedName name="Print_Area_Reset">OFFSET('To Do List'!$A:$H,0,0,COUNTA('To Do List'!$B:$B)+5)</definedName>
-    <definedName name="valHEnd">'Settings &amp; Calculations'!$C$18</definedName>
-    <definedName name="valHStart">'Settings &amp; Calculations'!$C$17</definedName>
+    <definedName name="valHEnd">#REF!</definedName>
+    <definedName name="valHStart">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,23 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>To be completed by:</t>
-  </si>
-  <si>
     <t>Deadline:</t>
   </si>
   <si>
-    <t>Highlight Activities</t>
-  </si>
-  <si>
-    <t>No Highlight</t>
-  </si>
-  <si>
     <t>Activity</t>
   </si>
   <si>
@@ -91,70 +81,6 @@
   </si>
   <si>
     <t>Literature Review</t>
-  </si>
-  <si>
-    <t>Paperwork</t>
-  </si>
-  <si>
-    <t>Start After Task B is Complete</t>
-  </si>
-  <si>
-    <t>Hand-off</t>
-  </si>
-  <si>
-    <t>Follow-up</t>
-  </si>
-  <si>
-    <t>Highlight Settings</t>
-  </si>
-  <si>
-    <t>The tables below store settings and calculations for the Highlight Activities drop down list.
-Any changes could result in errors or loss of functionality.</t>
-  </si>
-  <si>
-    <t>Interval:</t>
-  </si>
-  <si>
-    <t>Start:</t>
-  </si>
-  <si>
-    <t>End:</t>
-  </si>
-  <si>
-    <t>Due:</t>
-  </si>
-  <si>
-    <t>This Week</t>
-  </si>
-  <si>
-    <t>This Month</t>
-  </si>
-  <si>
-    <t>This Quarter</t>
-  </si>
-  <si>
-    <t>This Year</t>
-  </si>
-  <si>
-    <t>Last Week</t>
-  </si>
-  <si>
-    <t>Last Month</t>
-  </si>
-  <si>
-    <t>Last Quarter</t>
-  </si>
-  <si>
-    <t>Last Year</t>
-  </si>
-  <si>
-    <t>Selected Highlight:</t>
-  </si>
-  <si>
-    <t>Highlight Start</t>
-  </si>
-  <si>
-    <t>Highlight End</t>
   </si>
   <si>
     <t>Diabetic Retinopathy Prediction</t>
@@ -185,15 +111,46 @@
     <t>GitHub Repo will be managed by Ayush. 
 https://github.com/ayumahapat0/diabetic_retinopathy_prediction
 Access given to each member</t>
+  </si>
+  <si>
+    <t>Image Pre-Processing</t>
+  </si>
+  <si>
+    <t>Data Splitting</t>
+  </si>
+  <si>
+    <t>Keith</t>
+  </si>
+  <si>
+    <t>First Progress Report</t>
+  </si>
+  <si>
+    <t>Final Submission - Code</t>
+  </si>
+  <si>
+    <t>Final Submission - Paper</t>
+  </si>
+  <si>
+    <t>Introduction, Methods, Results, Conclusions, and Works cited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Progress Report </t>
+  </si>
+  <si>
+    <t>The final progress report is due two weeks before the final submission. 
+For the code portion, please submit all code as it currently stands. 
+For the written portion, write a (brief) description of what you have already completed and what more you plan to do before the final submission.</t>
+  </si>
+  <si>
+    <t>The first progress report is due roughly one month before the project.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
@@ -258,14 +215,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,19 +255,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -322,51 +267,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -378,73 +288,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -456,21 +308,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -478,56 +327,59 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -538,6 +390,27 @@
     <cellStyle name="Title" xfId="3" builtinId="15" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -552,26 +425,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Tahoma"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -762,13 +615,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblToDoList" displayName="tblToDoList" ref="B7:G16" headerRowDxfId="11" dataDxfId="10" totalsRowDxfId="9">
-  <autoFilter ref="B7:G16" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblToDoList" displayName="tblToDoList" ref="B7:G21" headerRowDxfId="11" dataDxfId="10" totalsRowDxfId="9">
+  <autoFilter ref="B7:G21" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -781,7 +630,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Due By" dataDxfId="7"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Owner" dataDxfId="6"/>
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Done" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Progress" dataDxfId="0" totalsRowDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Progress" dataDxfId="2" totalsRowDxfId="3"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Notes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="Project To Do List" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1024,295 +873,366 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6" style="34" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="51" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" style="44" customWidth="1"/>
-    <col min="7" max="7" width="67.7109375" style="24" customWidth="1"/>
-    <col min="8" max="8" width="6" style="34" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="34"/>
+    <col min="1" max="1" width="6" style="13" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="29" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="22" customWidth="1"/>
+    <col min="7" max="7" width="120.7109375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="6" style="13" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="35" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B2" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
+    <row r="2" spans="1:8" s="14" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="B2" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:8" s="15" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="21">
+        <v>46128</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" s="15" customFormat="1" ht="60.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="26" t="s">
+      <c r="C7" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="43">
-        <v>46125</v>
-      </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="28" t="s">
+      <c r="D7" s="22" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" s="36" customFormat="1" ht="60.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="34"/>
-    </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="24" t="s">
+      <c r="E7" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="F7" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="H7" s="13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="C8" s="10">
+        <v>46057</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="E8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="F8" s="24">
+        <v>1</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10">
+        <v>46057</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="24">
+        <v>1</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="10">
+        <v>46057</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="24">
+        <v>1</v>
+      </c>
+      <c r="G10" s="32"/>
+    </row>
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="10">
+        <v>46079</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="24">
+        <v>1</v>
+      </c>
+      <c r="G11" s="32"/>
+    </row>
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="11">
+        <v>46091</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="26">
+        <v>1</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11">
+        <v>46091</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="11">
+        <v>46092</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="26">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="11">
+        <v>46092</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="26">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="16"/>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="16"/>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="11">
+        <v>46093</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26">
+        <v>0.4</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="60" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="12">
+        <f>C20-14</f>
+        <v>46097</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="31">
-        <v>46057</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="46">
-        <v>1</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="31">
-        <v>46057</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="46">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="31">
-        <v>46057</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="46">
-        <v>1</v>
-      </c>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="31">
-        <v>46079</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="46">
-        <v>1</v>
-      </c>
-      <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="32">
-        <v>46091</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="48">
-        <v>1</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="32">
-        <f ca="1">TODAY()+45</f>
-        <v>46138</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="48"/>
-      <c r="F13" s="48">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="33">
-        <f ca="1">TODAY()+55</f>
-        <v>46148</v>
-      </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50">
+      <c r="G19" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+      <c r="B20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="12">
+        <v>46111</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28">
         <v>0</v>
       </c>
-      <c r="G14" s="30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="33">
-        <f ca="1">TODAY()+70</f>
-        <v>46163</v>
-      </c>
-      <c r="D15" s="49"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50">
-        <v>0.25</v>
-      </c>
-      <c r="G15" s="30"/>
-    </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="33">
-        <f ca="1">TODAY()+90</f>
-        <v>46183</v>
-      </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="30"/>
-    </row>
-    <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="G20" s="31"/>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="12">
+        <v>46111</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28">
+        <v>0</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1381,40 +1301,20 @@
     <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="99" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="100" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:G16">
-    <cfRule type="expression" dxfId="2" priority="2">
+  <conditionalFormatting sqref="B8:G21">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND($C8&gt;=valHStart, $C8&lt;=valHEnd)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="Select which period to automatically highlight using the dropdown in this cell._x000a__x000a_Dropdown options are auto generated using the Settings &amp; Calculations Tab." sqref="G5" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>lstToDoHighlights</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F8:F16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"0%,10%,20%,25%,30%,35%,40%,45%,50%,55%,60%,65%,70%,75%,80%,85%,90%,95%,100%"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Use this template to keep track of your To Do List for your project._x000a__x000a_Enter activities in the table below. Row will be highlighted based on selection in cell G5._x000a_" sqref="A1" xr:uid="{EEF73721-2F2D-4F08-9603-1D15DF71F893}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Title of the worksheet is in this cell" sqref="B2:G2" xr:uid="{7754D0E4-1946-486F-B610-8E7B3FDE16FB}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter name in this cell" sqref="B5" xr:uid="{AED8AA14-3825-4B4B-96E0-45C4A4552251}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter project deadline in this cell" sqref="E5" xr:uid="{DADDE291-E87A-4EC2-BF3F-B17A579D228F}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter project name in this cell" sqref="B6" xr:uid="{AD68667F-44E1-475E-958D-F9E89DCD65C6}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter activity name in this column under this heading" sqref="B7" xr:uid="{E36C98EB-DAB8-4911-B007-D406DD477ADA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter due date in this column under this heading" sqref="C7" xr:uid="{CE26D4E0-2F21-4AFA-88A2-485369645B4B}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter budget in this column under this heading" sqref="D7" xr:uid="{8B7CBACD-A3AA-42BB-AB9D-794B2A4EE2B9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter progress percentage in this column under this heading" sqref="F7" xr:uid="{E4F17B65-CE2D-4877-8C15-8CEDF9F8BB69}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:E16" xr:uid="{2755D52C-6EE9-4103-B46A-50B41A329A5A}">
-      <formula1>"YES"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter notes in this column under this heading" sqref="G7" xr:uid="{2979BFC6-287A-421D-8D8A-913AF66144C0}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter completed status of activity in this column under this heading using the dropdown." sqref="E7" xr:uid="{8D82205A-6ECD-483C-8ADC-3EA818EAB0C0}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:D16" xr:uid="{4D34D3F1-9CA7-44F3-8B43-DACDF3F3E7B5}">
-      <formula1>"Ayush, Keith, Tanay, All"</formula1>
-    </dataValidation>
-  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -1424,406 +1324,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Sheet2">
-    <tabColor theme="9"/>
-    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F100"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="6" style="34" customWidth="1"/>
-    <col min="2" max="2" width="30" style="34" customWidth="1"/>
-    <col min="3" max="3" width="36" style="34" customWidth="1"/>
-    <col min="4" max="4" width="40" style="34" customWidth="1"/>
-    <col min="5" max="5" width="38" style="34" customWidth="1"/>
-    <col min="6" max="6" width="6" style="34" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="34"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="34" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="35" customFormat="1" ht="99.95" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A2" s="1"/>
-      <c r="B2" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-    </row>
-    <row r="3" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
-      <c r="B4" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-    </row>
-    <row r="5" spans="1:6" s="36" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="8" t="str">
-        <f>B5</f>
-        <v>No Highlight</v>
-      </c>
-      <c r="F5" s="24"/>
-    </row>
-    <row r="6" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="11">
-        <f ca="1">TODAY()-WEEKDAY(TODAY(),2)+1</f>
-        <v>46090</v>
-      </c>
-      <c r="D7" s="11">
-        <f ca="1">C7+6</f>
-        <v>46096</v>
-      </c>
-      <c r="E7" s="10" t="str">
-        <f ca="1">B7&amp;" ["&amp;TEXT(C7,"d mmm")&amp;" - "&amp;TEXT(D7,"d mmm")&amp;"]"</f>
-        <v>This Week [9 Mar - 15 Mar]</v>
-      </c>
-      <c r="F7" s="24"/>
-    </row>
-    <row r="8" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7"/>
-      <c r="B8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="11">
-        <f ca="1">EOMONTH(TODAY(),-1)+1</f>
-        <v>46082</v>
-      </c>
-      <c r="D8" s="11">
-        <f ca="1">EDATE(C8,1)-1</f>
-        <v>46112</v>
-      </c>
-      <c r="E8" s="10" t="str">
-        <f ca="1">B8&amp;" ["&amp;TEXT(C8,"d")&amp;" - "&amp;TEXT(D8,"d, mmm")&amp;"]"</f>
-        <v>This Month [1 - 31, Mar]</v>
-      </c>
-      <c r="F8" s="24"/>
-    </row>
-    <row r="9" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7"/>
-      <c r="B9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="11">
-        <f ca="1">DATE(YEAR(TODAY()),INT(MONTH(TODAY())/3)+1,1)</f>
-        <v>46054</v>
-      </c>
-      <c r="D9" s="11">
-        <f ca="1">EDATE(C9,4)-1</f>
-        <v>46173</v>
-      </c>
-      <c r="E9" s="10" t="str">
-        <f ca="1">B9&amp;" ["&amp;TEXT(C9,"d mmm")&amp;" - "&amp;TEXT(D9,"d mmm")&amp;"]"</f>
-        <v>This Quarter [1 Feb - 31 May]</v>
-      </c>
-      <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7"/>
-      <c r="B10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="13">
-        <f ca="1">DATE(YEAR(TODAY()),1,1)</f>
-        <v>46023</v>
-      </c>
-      <c r="D10" s="13">
-        <f ca="1">EDATE(C10,12)-1</f>
-        <v>46387</v>
-      </c>
-      <c r="E10" s="12" t="str">
-        <f ca="1">B10&amp;" ["&amp;TEXT(C10,"yyyy")&amp;"]"</f>
-        <v>This Year [2026]</v>
-      </c>
-      <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7"/>
-      <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="4" t="str">
-        <f>B11</f>
-        <v>Interval:</v>
-      </c>
-      <c r="F11" s="24"/>
-    </row>
-    <row r="12" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7"/>
-      <c r="B12" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="16">
-        <f ca="1">C7-7</f>
-        <v>46083</v>
-      </c>
-      <c r="D12" s="16">
-        <f ca="1">C12+6</f>
-        <v>46089</v>
-      </c>
-      <c r="E12" s="15" t="str">
-        <f ca="1">B12&amp;" ["&amp;TEXT(C12,"d mmm")&amp;" - "&amp;TEXT(D12,"d mmm")&amp;"]"</f>
-        <v>Last Week [2 Mar - 8 Mar]</v>
-      </c>
-      <c r="F12" s="24"/>
-    </row>
-    <row r="13" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="16">
-        <f ca="1">EDATE(C8,-1)</f>
-        <v>46054</v>
-      </c>
-      <c r="D13" s="16">
-        <f ca="1">EDATE(C13,1)-1</f>
-        <v>46081</v>
-      </c>
-      <c r="E13" s="15" t="str">
-        <f ca="1">B13&amp;" ["&amp;TEXT(C13,"d")&amp;" - "&amp;TEXT(D13,"d, mmm")&amp;"]"</f>
-        <v>Last Month [1 - 28, Feb]</v>
-      </c>
-      <c r="F13" s="24"/>
-    </row>
-    <row r="14" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7"/>
-      <c r="B14" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="16">
-        <f ca="1">EDATE(C9,-3)</f>
-        <v>45962</v>
-      </c>
-      <c r="D14" s="16">
-        <f ca="1">EDATE(C14,3)-1</f>
-        <v>46053</v>
-      </c>
-      <c r="E14" s="15" t="str">
-        <f ca="1">B14&amp;" ["&amp;TEXT(C14,"d mmm")&amp;" - "&amp;TEXT(D14,"d mmm")&amp;"]"</f>
-        <v>Last Quarter [1 Nov - 31 Jan]</v>
-      </c>
-      <c r="F14" s="24"/>
-    </row>
-    <row r="15" spans="1:6" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="18">
-        <f ca="1">EDATE(C10,-12)</f>
-        <v>45658</v>
-      </c>
-      <c r="D15" s="18">
-        <f ca="1">EDATE(C15,12)-1</f>
-        <v>46022</v>
-      </c>
-      <c r="E15" s="17" t="str">
-        <f>B15</f>
-        <v>Last Year</v>
-      </c>
-      <c r="F15" s="24"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="19">
-        <f>IFERROR(MATCH(HighlightActivities,lstToDoHighlights,0),"")</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="19" t="str">
-        <f>HighlightActivities</f>
-        <v>No Highlight</v>
-      </c>
-      <c r="E16" s="19" t="b">
-        <f>ISNUMBER(INDEX($C$5:$C$15,C16))</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="24"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="21" t="str">
-        <f>IFERROR(IF(C16=1,"",IF(E16,INDEX($C$5:$C$15,$C$16),"")),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="24"/>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="23" t="str">
-        <f>IFERROR(IF(C16=1,"",IF(E16,INDEX($D$5:$D$15,$C$16),"")),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="24"/>
-    </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="E8 E13" formula="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2139,29 +1657,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76FDD323-8E7B-49B7-A576-85D534BC045A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C02396-02E5-4855-9EEB-E6D78D6179A2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2189,15 +1707,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C02396-02E5-4855-9EEB-E6D78D6179A2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76FDD323-8E7B-49B7-A576-85D534BC045A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/FAI Project Tracker.xlsx
+++ b/FAI Project Tracker.xlsx
@@ -147,7 +147,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +179,12 @@
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -254,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -331,9 +337,6 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="6" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -346,11 +349,11 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="7" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -688,14 +691,14 @@
   <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="33" width="6.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="34" width="38.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="34" width="13.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="33" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="33" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="35" width="15.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="33" width="120.7192857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="33" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="32" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="33" width="38.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="33" width="13.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="32" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="32" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="34" width="15.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="32" width="120.7192857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="32" width="6.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
@@ -747,7 +750,7 @@
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="21">
       <c r="A5" s="1"/>
       <c r="B5" s="15">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
@@ -920,7 +923,7 @@
       </c>
       <c r="H13" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="21">
       <c r="A14" s="17"/>
       <c r="B14" s="22" t="s">
         <v>23</v>
@@ -940,7 +943,7 @@
       <c r="G14" s="25"/>
       <c r="H14" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="21">
       <c r="A15" s="17"/>
       <c r="B15" s="22" t="s">
         <v>25</v>
@@ -960,7 +963,7 @@
       <c r="G15" s="25"/>
       <c r="H15" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="21">
       <c r="A16" s="17"/>
       <c r="B16" s="22" t="s">
         <v>26</v>
@@ -968,10 +971,10 @@
       <c r="C16" s="22">
         <v>46118</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="23" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="24">
@@ -980,7 +983,7 @@
       <c r="G16" s="25"/>
       <c r="H16" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="21">
       <c r="A17" s="17"/>
       <c r="B17" s="22" t="s">
         <v>27</v>
@@ -988,10 +991,10 @@
       <c r="C17" s="22">
         <v>46124</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="23" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="24">
@@ -1000,7 +1003,7 @@
       <c r="G17" s="25"/>
       <c r="H17" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="21">
       <c r="A18" s="17"/>
       <c r="B18" s="22" t="s">
         <v>29</v>
@@ -1020,904 +1023,904 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="64.5">
       <c r="A19" s="17"/>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <f>C20-14</f>
         <v>25568.791666666668</v>
       </c>
-      <c r="D19" s="28" t="s">
+      <c r="D19" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29">
+      <c r="E19" s="28"/>
+      <c r="F19" s="28">
         <v>1</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G19" s="29" t="s">
         <v>32</v>
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="21">
       <c r="A20" s="17"/>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>46111</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29">
+      <c r="E20" s="28"/>
+      <c r="F20" s="28">
         <v>1</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="29" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="21">
       <c r="A21" s="17"/>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>46111</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D21" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29">
+      <c r="E21" s="28"/>
+      <c r="F21" s="28">
         <v>1</v>
       </c>
-      <c r="G21" s="30" t="s">
+      <c r="G21" s="29" t="s">
         <v>36</v>
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="32"/>
+      <c r="F22" s="31"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="32"/>
+      <c r="F23" s="31"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="32"/>
+      <c r="F24" s="31"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="30">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="32"/>
+      <c r="F25" s="31"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="30">
       <c r="A26" s="1"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="32"/>
+      <c r="F26" s="31"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="30">
       <c r="A27" s="1"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="32"/>
+      <c r="F27" s="31"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="30">
       <c r="A28" s="1"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="32"/>
+      <c r="F28" s="31"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="30">
       <c r="A29" s="1"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="32"/>
+      <c r="F29" s="31"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="30">
       <c r="A30" s="1"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="32"/>
+      <c r="F30" s="31"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="30">
       <c r="A31" s="1"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="32"/>
+      <c r="F31" s="31"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="30">
       <c r="A32" s="1"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="32"/>
+      <c r="F32" s="31"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="30">
       <c r="A33" s="1"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="32"/>
+      <c r="F33" s="31"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="30">
       <c r="A34" s="1"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="32"/>
+      <c r="F34" s="31"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="30">
       <c r="A35" s="1"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="32"/>
+      <c r="F35" s="31"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="30">
       <c r="A36" s="1"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="32"/>
+      <c r="F36" s="31"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="30">
       <c r="A37" s="1"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="32"/>
+      <c r="F37" s="31"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="30">
       <c r="A38" s="1"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="32"/>
+      <c r="F38" s="31"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="30">
       <c r="A39" s="1"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="32"/>
+      <c r="F39" s="31"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="30">
       <c r="A40" s="1"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="32"/>
+      <c r="F40" s="31"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="30">
       <c r="A41" s="1"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="32"/>
+      <c r="F41" s="31"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="30">
       <c r="A42" s="1"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="32"/>
+      <c r="F42" s="31"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="30">
       <c r="A43" s="1"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="32"/>
+      <c r="F43" s="31"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="30">
       <c r="A44" s="1"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="32"/>
+      <c r="F44" s="31"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="30">
       <c r="A45" s="1"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="32"/>
+      <c r="F45" s="31"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="30">
       <c r="A46" s="1"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="32"/>
+      <c r="F46" s="31"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="30">
       <c r="A47" s="1"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="32"/>
+      <c r="F47" s="31"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="30">
       <c r="A48" s="1"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="32"/>
+      <c r="F48" s="31"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="30">
       <c r="A49" s="1"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="32"/>
+      <c r="F49" s="31"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="30">
       <c r="A50" s="1"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="32"/>
+      <c r="F50" s="31"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="30">
       <c r="A51" s="1"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="32"/>
+      <c r="F51" s="31"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="30">
       <c r="A52" s="1"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="32"/>
+      <c r="F52" s="31"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="30">
       <c r="A53" s="1"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="32"/>
+      <c r="F53" s="31"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="30">
       <c r="A54" s="1"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="32"/>
+      <c r="F54" s="31"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="30">
       <c r="A55" s="1"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="32"/>
+      <c r="F55" s="31"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="30">
       <c r="A56" s="1"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="31"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="32"/>
+      <c r="F56" s="31"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="30">
       <c r="A57" s="1"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="31"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="32"/>
+      <c r="F57" s="31"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="30">
       <c r="A58" s="1"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="32"/>
+      <c r="F58" s="31"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="30">
       <c r="A59" s="1"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="32"/>
+      <c r="F59" s="31"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="30">
       <c r="A60" s="1"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="32"/>
+      <c r="F60" s="31"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="30">
       <c r="A61" s="1"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="32"/>
+      <c r="F61" s="31"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="30">
       <c r="A62" s="1"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="32"/>
+      <c r="F62" s="31"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="30">
       <c r="A63" s="1"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="31"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="32"/>
+      <c r="F63" s="31"/>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="30">
       <c r="A64" s="1"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="32"/>
+      <c r="F64" s="31"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="30">
       <c r="A65" s="1"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="31"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="32"/>
+      <c r="F65" s="31"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="30">
       <c r="A66" s="1"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="31"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="32"/>
+      <c r="F66" s="31"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="30">
       <c r="A67" s="1"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="32"/>
+      <c r="F67" s="31"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="30">
       <c r="A68" s="1"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="32"/>
+      <c r="F68" s="31"/>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="30">
       <c r="A69" s="1"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="31"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="32"/>
+      <c r="F69" s="31"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="30">
       <c r="A70" s="1"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="32"/>
+      <c r="F70" s="31"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="30">
       <c r="A71" s="1"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="32"/>
+      <c r="F71" s="31"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="30">
       <c r="A72" s="1"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="32"/>
+      <c r="F72" s="31"/>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="30">
       <c r="A73" s="1"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="31"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="32"/>
+      <c r="F73" s="31"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="30">
       <c r="A74" s="1"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="31"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="32"/>
+      <c r="F74" s="31"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="30">
       <c r="A75" s="1"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="31"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="32"/>
+      <c r="F75" s="31"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="30">
       <c r="A76" s="1"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="31"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="32"/>
+      <c r="F76" s="31"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="30">
       <c r="A77" s="1"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="31"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="32"/>
+      <c r="F77" s="31"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="30">
       <c r="A78" s="1"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="31"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="32"/>
+      <c r="F78" s="31"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="30">
       <c r="A79" s="1"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="31"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="32"/>
+      <c r="F79" s="31"/>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="30">
       <c r="A80" s="1"/>
-      <c r="B80" s="31"/>
-      <c r="C80" s="31"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="32"/>
+      <c r="F80" s="31"/>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="30">
       <c r="A81" s="1"/>
-      <c r="B81" s="31"/>
-      <c r="C81" s="31"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="30"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="32"/>
+      <c r="F81" s="31"/>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="30">
       <c r="A82" s="1"/>
-      <c r="B82" s="31"/>
-      <c r="C82" s="31"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="32"/>
+      <c r="F82" s="31"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="30">
       <c r="A83" s="1"/>
-      <c r="B83" s="31"/>
-      <c r="C83" s="31"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="32"/>
+      <c r="F83" s="31"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="30">
       <c r="A84" s="1"/>
-      <c r="B84" s="31"/>
-      <c r="C84" s="31"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="32"/>
+      <c r="F84" s="31"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="30">
       <c r="A85" s="1"/>
-      <c r="B85" s="31"/>
-      <c r="C85" s="31"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="32"/>
+      <c r="F85" s="31"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="30">
       <c r="A86" s="1"/>
-      <c r="B86" s="31"/>
-      <c r="C86" s="31"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="32"/>
+      <c r="F86" s="31"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="30">
       <c r="A87" s="1"/>
-      <c r="B87" s="31"/>
-      <c r="C87" s="31"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="32"/>
+      <c r="F87" s="31"/>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="30">
       <c r="A88" s="1"/>
-      <c r="B88" s="31"/>
-      <c r="C88" s="31"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="32"/>
+      <c r="F88" s="31"/>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="30">
       <c r="A89" s="1"/>
-      <c r="B89" s="31"/>
-      <c r="C89" s="31"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="32"/>
+      <c r="F89" s="31"/>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="30">
       <c r="A90" s="1"/>
-      <c r="B90" s="31"/>
-      <c r="C90" s="31"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="32"/>
+      <c r="F90" s="31"/>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="30">
       <c r="A91" s="1"/>
-      <c r="B91" s="31"/>
-      <c r="C91" s="31"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="32"/>
+      <c r="F91" s="31"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="30">
       <c r="A92" s="1"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="31"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="32"/>
+      <c r="F92" s="31"/>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="30">
       <c r="A93" s="1"/>
-      <c r="B93" s="31"/>
-      <c r="C93" s="31"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="32"/>
+      <c r="F93" s="31"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="30">
       <c r="A94" s="1"/>
-      <c r="B94" s="31"/>
-      <c r="C94" s="31"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="32"/>
+      <c r="F94" s="31"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="30">
       <c r="A95" s="1"/>
-      <c r="B95" s="31"/>
-      <c r="C95" s="31"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="32"/>
+      <c r="F95" s="31"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="30">
       <c r="A96" s="1"/>
-      <c r="B96" s="31"/>
-      <c r="C96" s="31"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="32"/>
+      <c r="F96" s="31"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="30">
       <c r="A97" s="1"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="31"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="32"/>
+      <c r="F97" s="31"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="30">
       <c r="A98" s="1"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="31"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="32"/>
+      <c r="F98" s="31"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="30">
       <c r="A99" s="1"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="31"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="32"/>
+      <c r="F99" s="31"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="30">
       <c r="A100" s="1"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="31"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="32"/>
+      <c r="F100" s="31"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="30">
       <c r="A101" s="1"/>
-      <c r="B101" s="31"/>
-      <c r="C101" s="31"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="32"/>
+      <c r="F101" s="31"/>
       <c r="G101" s="1"/>
       <c r="H101" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="30">
       <c r="A102" s="1"/>
-      <c r="B102" s="31"/>
-      <c r="C102" s="31"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="32"/>
+      <c r="F102" s="31"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="30">
       <c r="A103" s="1"/>
-      <c r="B103" s="31"/>
-      <c r="C103" s="31"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="32"/>
+      <c r="F103" s="31"/>
       <c r="G103" s="1"/>
       <c r="H103" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="30">
       <c r="A104" s="1"/>
-      <c r="B104" s="31"/>
-      <c r="C104" s="31"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="32"/>
+      <c r="F104" s="31"/>
       <c r="G104" s="1"/>
       <c r="H104" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="30">
       <c r="A105" s="1"/>
-      <c r="B105" s="31"/>
-      <c r="C105" s="31"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="32"/>
+      <c r="F105" s="31"/>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
     </row>
